--- a/ARA July Data Wait Lists 2025.xlsx
+++ b/ARA July Data Wait Lists 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tewaka-my.sharepoint.com/personal/bir0061_arastudent_ac_nz/Documents/BCDE214 Database Administration/Assessment1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="367" documentId="11_3C15A38FDE5D0C97453EEB9F2C7EF84A6723868C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48144E69-F1CF-4E80-AE5C-014DD7A7FCAD}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="11_3C15A38FDE5D0C97453EEB9F2C7EF84A6723868C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E115237-BFC3-40A0-8D80-B8175A140286}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ARA July Data Wait Lists 2025.xlsx
+++ b/ARA July Data Wait Lists 2025.xlsx
@@ -34,6 +34,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
